--- a/User_Data/Watchlists/aus_econ/aus_econ.xlsx
+++ b/User_Data/Watchlists/aus_econ/aus_econ.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,50 @@
         </is>
       </c>
       <c r="D63" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>A2603039T</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A2603039T</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Quarterly Index ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private ;  All industries ;</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>A2603989W</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A2603989W</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Quarterly Index ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Public ;  All industries ;</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1831,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE19"/>
+  <dimension ref="A1:CG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2243,6 +2287,16 @@
       <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>australia/private-debt-to-gdp</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>A2603039T</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>A2603989W</t>
         </is>
       </c>
     </row>
@@ -2638,6 +2692,16 @@
         </is>
       </c>
       <c r="CE2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -2967,6 +3031,8 @@
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3288,6 +3354,8 @@
       <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -3681,6 +3749,16 @@
         </is>
       </c>
       <c r="CE5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -4014,6 +4092,8 @@
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4107,6 +4187,8 @@
       <c r="CC7" t="inlineStr"/>
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4522,6 +4604,16 @@
       <c r="CE8" t="inlineStr">
         <is>
           <t>tedata</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
         </is>
       </c>
     </row>
@@ -4621,6 +4713,8 @@
       <c r="CC9" t="inlineStr"/>
       <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -4830,6 +4924,8 @@
       <c r="CC10" t="inlineStr"/>
       <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -5037,6 +5133,8 @@
       <c r="CC11" t="inlineStr"/>
       <c r="CD11" t="inlineStr"/>
       <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -5128,6 +5226,8 @@
       <c r="CC12" t="inlineStr"/>
       <c r="CD12" t="inlineStr"/>
       <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -5337,6 +5437,8 @@
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
       <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -5546,6 +5648,8 @@
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
       <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -5755,6 +5859,8 @@
       <c r="CC15" t="inlineStr"/>
       <c r="CD15" t="inlineStr"/>
       <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -5844,6 +5950,8 @@
       <c r="CC16" t="inlineStr"/>
       <c r="CD16" t="inlineStr"/>
       <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -6261,6 +6369,16 @@
           <t>australia/private-debt-to-gdp</t>
         </is>
       </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>A2603039T</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>A2603989W</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -6676,6 +6794,16 @@
       <c r="CE18" t="inlineStr">
         <is>
           <t>australia/private-debt-to-gdp</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>A2603039T</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>A2603989W</t>
         </is>
       </c>
     </row>
@@ -6767,6 +6895,8 @@
       <c r="CC19" t="inlineStr"/>
       <c r="CD19" t="inlineStr"/>
       <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/User_Data/Watchlists/aus_econ/aus_econ.xlsx
+++ b/User_Data/Watchlists/aus_econ/aus_econ.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1793,28 @@
         </is>
       </c>
       <c r="D62" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Quarterly Index ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private and Public ;  All industries ;</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
